--- a/artfynd/A 63533-2025 artfynd.xlsx
+++ b/artfynd/A 63533-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62689591</v>
+        <v>62689540</v>
       </c>
       <c r="B2" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Späd hårgräsmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Brachythecium tommasinii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Sendtn. ex Boulay) Ignatov &amp; Huttunen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496756.1782026831</v>
+        <v>496765</v>
       </c>
       <c r="R2" t="n">
-        <v>6594212.002916113</v>
+        <v>6594207</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2016-10-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövblandad granskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Asplåga</t>
+          <t>Kalkhaltig klippa</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,50 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62689550</v>
+        <v>89342450</v>
       </c>
       <c r="B3" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>349</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Späd hårgräsmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Brachythecium tommasinii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Sendtn. ex Boulay) Ignatov &amp; Huttunen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knapptorp, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496839.1263389583</v>
+        <v>496775</v>
       </c>
       <c r="R3" t="n">
-        <v>6594227.170079921</v>
+        <v>6594216</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,23 +870,28 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>kalkgranskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Kalkhaltig klippa</t>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -927,53 +902,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62689566</v>
+        <v>89825476</v>
       </c>
       <c r="B4" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>349</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Späd hårgräsmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Brachythecium tommasinii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Sendtn. ex Boulay) Ignatov &amp; Huttunen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knapptorp, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496839.144665781</v>
+        <v>496687</v>
       </c>
       <c r="R4" t="n">
-        <v>6594249.010632069</v>
+        <v>6594148</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,23 +986,23 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Kalkhaltig klippa</t>
+          <t>Kalksten i kalkbrott</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1053,37 +1013,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62689552</v>
+        <v>62689591</v>
       </c>
       <c r="B5" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2668</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496686.9895451624</v>
+        <v>496756</v>
       </c>
       <c r="R5" t="n">
-        <v>6594222.221592834</v>
+        <v>6594212</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,22 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,12 +1097,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bäckdal</t>
+          <t>Lövblandad granskog</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Kalkhaltig klippa</t>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62689540</v>
+        <v>88166473</v>
       </c>
       <c r="B6" t="n">
-        <v>92917</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,34 +1135,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>349</v>
+        <v>1988</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Späd hårgräsmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Brachythecium tommasinii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sendtn. ex Boulay) Ignatov &amp; Huttunen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knapptorp, Vstm</t>
+          <t>Knapptorpsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496764.8235394855</v>
+        <v>496796</v>
       </c>
       <c r="R6" t="n">
-        <v>6594206.916240814</v>
+        <v>6594266</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,22 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-10-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,23 +1208,18 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Kalkhaltig klippa</t>
+          <t>medelålders granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1305,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62689565</v>
+        <v>62689560</v>
       </c>
       <c r="B7" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496702.1896469777</v>
+        <v>496692</v>
       </c>
       <c r="R7" t="n">
-        <v>6594149.066729478</v>
+        <v>6594147</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1378,19 +1298,9 @@
           <t>2016-10-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,15 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62689569</v>
+        <v>89825469</v>
       </c>
       <c r="B8" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,37 +1352,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2666</v>
+        <v>2609</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knapptorp, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496707.8163466352</v>
+        <v>496697</v>
       </c>
       <c r="R8" t="n">
-        <v>6594183.09311023</v>
+        <v>6594157</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,22 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-10-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,23 +1425,23 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Bäckdal</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Kalkhaltig klippa</t>
+          <t>Kalklodyta i bäckkanten</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1557,15 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89342445</v>
+        <v>62689567</v>
       </c>
       <c r="B9" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,25 +1472,25 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496707.8172344547</v>
+        <v>496705</v>
       </c>
       <c r="R9" t="n">
-        <v>6594184.108964521</v>
+        <v>6594120</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1627,22 +1517,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,23 +1536,23 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>Granskog i brant</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1683,15 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89342452</v>
+        <v>62689568</v>
       </c>
       <c r="B10" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,34 +1574,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496777.0427181798</v>
+        <v>496693</v>
       </c>
       <c r="R10" t="n">
-        <v>6594216.048394169</v>
+        <v>6594148</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1753,22 +1628,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,23 +1647,23 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1809,15 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89342448</v>
+        <v>62689569</v>
       </c>
       <c r="B11" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,34 +1685,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496771.9581475001</v>
+        <v>496708</v>
       </c>
       <c r="R11" t="n">
-        <v>6594220.116130986</v>
+        <v>6594183</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1879,22 +1739,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1908,23 +1758,23 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>Bäckdal</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>Kalkhaltig klippa</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1935,15 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89342453</v>
+        <v>89342445</v>
       </c>
       <c r="B12" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,21 +1796,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2779</v>
+        <v>2666</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1975,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496777.0427181798</v>
+        <v>496708</v>
       </c>
       <c r="R12" t="n">
-        <v>6594216.048394169</v>
+        <v>6594184</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2008,28 +1853,17 @@
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2062,15 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89342441</v>
+        <v>89342454</v>
       </c>
       <c r="B13" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2102,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496707.8172344547</v>
+        <v>496750</v>
       </c>
       <c r="R13" t="n">
-        <v>6594184.108964521</v>
+        <v>6594195</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2135,21 +1964,11 @@
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2166,7 +1985,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2188,37 +2007,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89342450</v>
+        <v>89825479</v>
       </c>
       <c r="B14" t="n">
-        <v>92917</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>349</v>
+        <v>2666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Späd hårgräsmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Brachythecium tommasinii</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sendtn. ex Boulay) Ignatov &amp; Huttunen</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2228,13 +2042,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496775.007497067</v>
+        <v>496687</v>
       </c>
       <c r="R14" t="n">
-        <v>6594216.050136046</v>
+        <v>6594148</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2258,22 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2287,28 +2091,23 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>Kalksten i kalkbrott</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2319,15 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89342455</v>
+        <v>62689565</v>
       </c>
       <c r="B15" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2344,25 +2138,25 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496750.058071722</v>
+        <v>496702</v>
       </c>
       <c r="R15" t="n">
-        <v>6594195.246671954</v>
+        <v>6594149</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2389,22 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2418,23 +2202,23 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>lodyta</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2445,15 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89342459</v>
+        <v>62689566</v>
       </c>
       <c r="B16" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,34 +2240,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496684.9762300304</v>
+        <v>496839</v>
       </c>
       <c r="R16" t="n">
-        <v>6594247.111477259</v>
+        <v>6594249</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2515,22 +2294,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2544,18 +2313,23 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Kalkhaltig klippa</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2566,15 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89342463</v>
+        <v>88403132</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2582,34 +2351,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken, Vstm</t>
+          <t>Knapptorpsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496663.1180307133</v>
+        <v>496702</v>
       </c>
       <c r="R17" t="n">
-        <v>6594269.987063182</v>
+        <v>6594160</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2636,22 +2405,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2665,18 +2424,18 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>kalkgranskog</t>
+          <t>block med kalkinslag</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2687,15 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89342454</v>
+        <v>89342441</v>
       </c>
       <c r="B18" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2703,21 +2457,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2727,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496750.058071722</v>
+        <v>496708</v>
       </c>
       <c r="R18" t="n">
-        <v>6594195.246671954</v>
+        <v>6594184</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2760,21 +2514,11 @@
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2791,7 +2535,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2816,12 +2560,7 @@
         <v>89342447</v>
       </c>
       <c r="B19" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2838,12 +2577,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2853,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496827.9138364378</v>
+        <v>496828</v>
       </c>
       <c r="R19" t="n">
-        <v>6594204.830886818</v>
+        <v>6594205</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2886,19 +2625,9 @@
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2939,15 +2668,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89342442</v>
+        <v>89342448</v>
       </c>
       <c r="B20" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2955,21 +2679,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2979,10 +2703,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496707.8172344547</v>
+        <v>496772</v>
       </c>
       <c r="R20" t="n">
-        <v>6594184.108964521</v>
+        <v>6594220</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3012,19 +2736,9 @@
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-10-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3065,15 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89342457</v>
+        <v>89342452</v>
       </c>
       <c r="B21" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,21 +2790,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3105,10 +2814,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496751.0572886221</v>
+        <v>496777</v>
       </c>
       <c r="R21" t="n">
-        <v>6594173.912859672</v>
+        <v>6594216</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3138,21 +2847,11 @@
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3165,6 +2864,11 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3186,50 +2890,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>87865984</v>
+        <v>89342455</v>
       </c>
       <c r="B22" t="n">
-        <v>90023</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3014</v>
+        <v>2667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Parasitporing</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antrodiella parasitica</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Vampola</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496828.4957705513</v>
+        <v>496750</v>
       </c>
       <c r="R22" t="n">
-        <v>6594291.684513621</v>
+        <v>6594195</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3256,22 +2955,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,18 +2974,23 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3307,15 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>88402987</v>
+        <v>89825475</v>
       </c>
       <c r="B23" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,34 +3012,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>2667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496709.3942452262</v>
+        <v>496687</v>
       </c>
       <c r="R23" t="n">
-        <v>6594242.010873985</v>
+        <v>6594148</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3377,22 +3066,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3406,18 +3085,23 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>bäckdal med lövblandskog</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Kalksten i kalkbrott</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3428,15 +3112,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>88402986</v>
+        <v>62689549</v>
       </c>
       <c r="B24" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3444,34 +3123,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>2668</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496700.1570593112</v>
+        <v>496725</v>
       </c>
       <c r="R24" t="n">
-        <v>6594152.116101265</v>
+        <v>6594118</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3498,22 +3177,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3527,18 +3196,23 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>blockig blandskog</t>
+          <t>Blandksog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3549,15 +3223,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>88166372</v>
+        <v>62689550</v>
       </c>
       <c r="B25" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3565,30 +3234,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>224364</v>
+        <v>2668</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496866.1719589293</v>
+        <v>496839</v>
       </c>
       <c r="R25" t="n">
-        <v>6594322.127635606</v>
+        <v>6594227</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3615,22 +3288,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3644,18 +3307,23 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Kalkhaltig klippa</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3666,50 +3334,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87865978</v>
+        <v>62689552</v>
       </c>
       <c r="B26" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496829.9892430371</v>
+        <v>496687</v>
       </c>
       <c r="R26" t="n">
-        <v>6594252.573754985</v>
+        <v>6594222</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3736,22 +3399,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3765,18 +3418,23 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>Bäckdal</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Kalkhaltig klippa</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3787,37 +3445,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>88403120</v>
+        <v>88403133</v>
       </c>
       <c r="B27" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>2668</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3827,10 +3480,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496669.2155225698</v>
+        <v>496700</v>
       </c>
       <c r="R27" t="n">
-        <v>6594260.839168705</v>
+        <v>6594152</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3860,21 +3513,11 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3886,7 +3529,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>lövrik blandskog</t>
+          <t>blockig blandskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3908,15 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>88403100</v>
+        <v>89342442</v>
       </c>
       <c r="B28" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3924,34 +3562,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496700.1570593112</v>
+        <v>496708</v>
       </c>
       <c r="R28" t="n">
-        <v>6594152.116101265</v>
+        <v>6594184</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3978,22 +3616,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4007,18 +3635,23 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>blockig blandskog</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4029,15 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>88403133</v>
+        <v>89825478</v>
       </c>
       <c r="B29" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4059,23 +3687,23 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496700.1570593112</v>
+        <v>496687</v>
       </c>
       <c r="R29" t="n">
-        <v>6594152.116101265</v>
+        <v>6594148</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4099,22 +3727,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4128,18 +3746,23 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>blockig blandskog</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Kalksten i kalkbrott</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4150,15 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>88403051</v>
+        <v>89825465</v>
       </c>
       <c r="B30" t="n">
-        <v>84606</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4166,37 +3784,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4852</v>
+        <v>2676</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kastanjefjällskivling</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepiota castanea</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496817.2057192553</v>
+        <v>496697</v>
       </c>
       <c r="R30" t="n">
-        <v>6594177.411888678</v>
+        <v>6594157</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4220,22 +3838,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4249,18 +3857,18 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>mossig stig</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4271,15 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>88403033</v>
+        <v>89342453</v>
       </c>
       <c r="B31" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4287,34 +3890,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>2779</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496708.3575566669</v>
+        <v>496777</v>
       </c>
       <c r="R31" t="n">
-        <v>6594220.171170251</v>
+        <v>6594216</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4341,22 +3944,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4365,23 +3958,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>bäckdal med lövblandskog</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4392,15 +3991,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>88402983</v>
+        <v>88403033</v>
       </c>
       <c r="B32" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4408,21 +4002,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4432,10 +4026,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496708.3575566669</v>
+        <v>496708</v>
       </c>
       <c r="R32" t="n">
-        <v>6594220.171170251</v>
+        <v>6594220</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4465,19 +4059,9 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,12 +4100,7 @@
         <v>88403034</v>
       </c>
       <c r="B33" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4553,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496709.3942452262</v>
+        <v>496709</v>
       </c>
       <c r="R33" t="n">
-        <v>6594242.010873985</v>
+        <v>6594242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4586,19 +4165,9 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4634,15 +4203,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121698034</v>
+        <v>89342465</v>
       </c>
       <c r="B34" t="n">
-        <v>97315</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4650,42 +4214,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220250</v>
+        <v>2813</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken uppströms banvallen., Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496681</v>
+        <v>496612</v>
       </c>
       <c r="R34" t="n">
-        <v>6594265</v>
+        <v>6594316</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4712,22 +4272,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4740,18 +4290,2051 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>89342459</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>496685</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6594247</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>87865984</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92580</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3014</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Parasitporing</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Antrodiella parasitica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vampola</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>496828</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6594292</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>88403140</v>
+      </c>
+      <c r="B37" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>496702</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6594160</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>blockig blandskog på kalk</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>87865917</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>496793</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6594265</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>88402982</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>496671</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6594166</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>blandskog i bäckdal</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>88402983</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>496708</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6594220</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>bäckdal med lövblandskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>88403051</v>
+      </c>
+      <c r="B41" t="n">
+        <v>86818</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4852</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kastanjefjällskivling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lepiota castanea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>496817</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6594177</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>mossig stig</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121698034</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken uppströms banvallen., Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>496681</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6594265</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>Anders Carlberg</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Anders Carlberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>87865978</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>496830</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6594253</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2020-09-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>88403119</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>496702</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6594160</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>blockig blandskog på kalk</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>88403120</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>496669</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6594261</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>lövrik blandskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>88402981</v>
+      </c>
+      <c r="B46" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>496702</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6594160</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>blockig blandskog på kalk</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>88403100</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>496700</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6594152</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>blockig blandskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>88403102</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>496671</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6594166</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>blandskog i bäckdal</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>89342463</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>496663</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6594270</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>88402986</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>496700</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6594152</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>blockig blandskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>88402987</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>496709</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6594242</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>bäckdal med lövblandskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>89342457</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>496751</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6594174</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>88166372</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>496866</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6594322</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63533-2025 artfynd.xlsx
+++ b/artfynd/A 63533-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689540</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689591</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166473</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689560</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825469</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689567</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689568</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689569</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342445</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342454</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825479</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689565</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689566</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2443,6 +2523,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403132</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2554,6 +2639,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342441</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2665,6 +2755,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342447</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2776,6 +2871,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342448</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2887,6 +2987,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342452</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2998,6 +3103,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342455</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3109,6 +3219,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825475</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3220,6 +3335,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689549</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3331,6 +3451,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689550</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3442,6 +3567,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689552</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3548,6 +3678,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403133</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3659,6 +3794,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342442</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3770,6 +3910,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825478</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3876,6 +4021,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825465</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3988,6 +4138,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342453</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4094,6 +4249,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403033</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4198,6 +4358,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403034</t>
         </is>
       </c>
     </row>
@@ -4311,6 +4476,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342465</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4417,6 +4587,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342459</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4523,6 +4698,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865984</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4629,6 +4809,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403140</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4739,6 +4924,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865917</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4845,6 +5035,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402982</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4951,6 +5146,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402983</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5057,6 +5257,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403051</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5173,6 +5378,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121698034</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5279,6 +5489,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865978</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5385,6 +5600,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403119</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5491,6 +5711,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403120</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5597,6 +5822,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402981</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5703,6 +5933,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403100</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5809,6 +6044,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403102</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5915,6 +6155,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342463</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6021,6 +6266,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402986</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6127,6 +6377,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402987</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6233,6 +6488,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342457</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6335,8 +6595,67 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166372</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>